--- a/assets/datas/feuille-centrage-template-v2.xlsx
+++ b/assets/datas/feuille-centrage-template-v2.xlsx
@@ -266,8 +266,16 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -287,7 +295,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -307,15 +315,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -333,14 +333,6 @@
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -448,10 +440,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0989697686201655"/>
-          <c:y val="0.0262793914246196"/>
-          <c:w val="0.708072960648539"/>
-          <c:h val="0.827877670201322"/>
+          <c:x val="0.0989781268473946"/>
+          <c:y val="0.0262834306793729"/>
+          <c:w val="0.70804830673085"/>
+          <c:h val="0.827697509990778"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -647,11 +639,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="25866025"/>
-        <c:axId val="26963442"/>
+        <c:axId val="35612949"/>
+        <c:axId val="63905872"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="25866025"/>
+        <c:axId val="35612949"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -694,15 +686,15 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26963442"/>
+        <c:crossAx val="63905872"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="26963442"/>
+        <c:axId val="63905872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="400"/>
+          <c:min val="200"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -744,7 +736,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25866025"/>
+        <c:crossAx val="35612949"/>
         <c:crosses val="min"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -821,9 +813,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>25200</xdr:colOff>
+      <xdr:colOff>24840</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>136800</xdr:rowOff>
+      <xdr:rowOff>151560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -832,7 +824,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5844960" y="922680"/>
-        <a:ext cx="4262760" cy="2342160"/>
+        <a:ext cx="4262400" cy="2341800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -959,368 +951,370 @@
   <dimension ref="A1:F58"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E1" s="1" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="5"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="5"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="5"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5"/>
-      <c r="C21" s="12"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="8"/>
       <c r="D21" s="13"/>
-      <c r="E21" s="5"/>
+      <c r="E21" s="7"/>
       <c r="F21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5"/>
-      <c r="C22" s="12"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="8"/>
       <c r="D22" s="15"/>
-      <c r="E22" s="5"/>
+      <c r="E22" s="7"/>
       <c r="F22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5"/>
-      <c r="C23" s="12"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="8"/>
       <c r="D23" s="15"/>
-      <c r="E23" s="5"/>
+      <c r="E23" s="7"/>
       <c r="F23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5"/>
-      <c r="C24" s="12"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="8"/>
       <c r="D24" s="13"/>
-      <c r="E24" s="5"/>
+      <c r="E24" s="7"/>
       <c r="F24" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="5"/>
-      <c r="C25" s="12"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="8"/>
       <c r="D25" s="13"/>
-      <c r="E25" s="5"/>
+      <c r="E25" s="7"/>
       <c r="F25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="5"/>
+      <c r="B26" s="7"/>
       <c r="C26" s="16"/>
       <c r="D26" s="15"/>
-      <c r="E26" s="5"/>
+      <c r="E26" s="7"/>
       <c r="F26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="5"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
       <c r="F27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="5"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="7"/>
       <c r="F28" s="14"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="20" t="s">
+      <c r="B52" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="5">
